--- a/backend/tests/fixtures/synthetic/template_filled.xlsx
+++ b/backend/tests/fixtures/synthetic/template_filled.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ada@example.com</t>
+          <t>ada@acme.example</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>acme.example.com</t>
+          <t>acme.example</t>
         </is>
       </c>
       <c r="V3" t="n">
@@ -716,7 +716,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>jose.muller@example.org</t>
+          <t>jose.muller@globex.example</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://globex.example.org</t>
+          <t>https://globex.example</t>
         </is>
       </c>
       <c r="V4" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>zoe@example.net</t>
+          <t>zoe@initech.example</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>linus@example.com</t>
+          <t>linus@umbrella.example</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
